--- a/Informe.xlsx
+++ b/Informe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebaa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206D0210-97A3-490A-B698-D375716491A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A309FF4-9220-440D-A828-2837FC632292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,12 +31,6 @@
     <t>Producto</t>
   </si>
   <si>
-    <t>Precio (CLP)</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
     <t>Martillos</t>
   </si>
   <si>
@@ -179,6 +173,12 @@
   </si>
   <si>
     <t>Cizallas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantidad en Stock	</t>
+  </si>
+  <si>
+    <t>Precio Unitario</t>
   </si>
 </sst>
 </file>
@@ -186,9 +186,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="_ [$$-340A]* #,##0_ ;_ [$$-340A]* \-#,##0_ ;_ [$$-340A]* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ [$$-340A]* #,##0_ ;_ [$$-340A]* \-#,##0_ ;_ [$$-340A]* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +213,14 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -254,18 +262,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,387 +579,394 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:E38"/>
+  <dimension ref="B2:G38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="3" max="3" width="37.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="4">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4">
+        <v>4000</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3456</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="4"/>
     </row>
     <row r="36" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4"/>
     </row>
     <row r="37" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4"/>
     </row>
     <row r="38" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>

--- a/Informe.xlsx
+++ b/Informe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebaa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A309FF4-9220-440D-A828-2837FC632292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7075FE-35EA-421F-8E9D-54CC4D739CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -188,7 +188,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ [$$-340A]* #,##0_ ;_ [$$-340A]* \-#,##0_ ;_ [$$-340A]* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +221,14 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="singleAccounting"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -262,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -275,6 +283,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,7 +649,9 @@
       <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>10</v>
+      </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -648,7 +661,9 @@
       <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3">
+        <v>11</v>
+      </c>
       <c r="E6" s="4"/>
     </row>
     <row r="7" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -658,7 +673,9 @@
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3">
+        <v>12</v>
+      </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -668,7 +685,9 @@
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3">
+        <v>3</v>
+      </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -678,18 +697,22 @@
       <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3">
+        <v>3</v>
+      </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="21" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="4"/>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
@@ -698,7 +721,9 @@
       <c r="C11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -708,7 +733,9 @@
       <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
       <c r="E12" s="4"/>
     </row>
     <row r="13" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -718,7 +745,9 @@
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
       <c r="E13" s="4"/>
     </row>
     <row r="14" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -728,7 +757,9 @@
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -738,7 +769,9 @@
       <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
       <c r="E15" s="4"/>
     </row>
     <row r="16" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -748,7 +781,9 @@
       <c r="C16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
       <c r="E16" s="4"/>
     </row>
     <row r="17" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -758,7 +793,9 @@
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
       <c r="E17" s="4"/>
     </row>
     <row r="18" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -768,7 +805,9 @@
       <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -778,7 +817,9 @@
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -788,7 +829,9 @@
       <c r="C20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
       <c r="E20" s="4"/>
     </row>
     <row r="21" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -798,7 +841,9 @@
       <c r="C21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
       <c r="E21" s="4"/>
     </row>
     <row r="22" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -808,7 +853,9 @@
       <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -818,7 +865,9 @@
       <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -828,7 +877,9 @@
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -838,7 +889,9 @@
       <c r="C25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -848,7 +901,9 @@
       <c r="C26" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -858,7 +913,9 @@
       <c r="C27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -868,7 +925,9 @@
       <c r="C28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
       <c r="E28" s="4"/>
     </row>
     <row r="29" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -878,7 +937,9 @@
       <c r="C29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -888,7 +949,9 @@
       <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -898,7 +961,9 @@
       <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
       <c r="E31" s="4"/>
     </row>
     <row r="32" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -908,7 +973,9 @@
       <c r="C32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -918,7 +985,9 @@
       <c r="C33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -928,7 +997,9 @@
       <c r="C34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="3"/>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
       <c r="E34" s="4"/>
     </row>
     <row r="35" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -938,7 +1009,9 @@
       <c r="C35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="3"/>
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
       <c r="E35" s="4"/>
     </row>
     <row r="36" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -948,7 +1021,9 @@
       <c r="C36" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
       <c r="E36" s="4"/>
     </row>
     <row r="37" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -958,7 +1033,9 @@
       <c r="C37" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3">
+        <v>1</v>
+      </c>
       <c r="E37" s="4"/>
     </row>
     <row r="38" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
@@ -968,11 +1045,14 @@
       <c r="C38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3">
+        <v>1</v>
+      </c>
       <c r="E38" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:E38" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Informe.xlsx
+++ b/Informe.xlsx
@@ -5,25 +5,26 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebaa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebaa\OneDrive\Desktop\ProyectoReal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7075FE-35EA-421F-8E9D-54CC4D739CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C47D12-E0ED-405B-8654-10E4A4AF6F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$E$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$E$33</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="62">
   <si>
     <t>Categoría</t>
   </si>
@@ -175,10 +176,40 @@
     <t>Cizallas</t>
   </si>
   <si>
-    <t xml:space="preserve">Cantidad en Stock	</t>
-  </si>
-  <si>
     <t>Precio Unitario</t>
+  </si>
+  <si>
+    <t>Cantidad en Stock</t>
+  </si>
+  <si>
+    <t>Martillo</t>
+  </si>
+  <si>
+    <t>Alicate</t>
+  </si>
+  <si>
+    <t>Herramientas</t>
+  </si>
+  <si>
+    <t>Llave francesa</t>
+  </si>
+  <si>
+    <t>Cemento</t>
+  </si>
+  <si>
+    <t>Contruccion</t>
+  </si>
+  <si>
+    <t>Yeso</t>
+  </si>
+  <si>
+    <t>Mortero</t>
+  </si>
+  <si>
+    <t>OSB</t>
+  </si>
+  <si>
+    <t>Esmalte al agua</t>
   </si>
 </sst>
 </file>
@@ -188,7 +219,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_ [$$-340A]* #,##0_ ;_ [$$-340A]* \-#,##0_ ;_ [$$-340A]* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,14 +252,6 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u val="singleAccounting"/>
-      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -276,14 +299,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -590,16 +613,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G38"/>
+  <dimension ref="B2:I33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.28515625" customWidth="1"/>
     <col min="4" max="4" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -607,10 +630,481 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>50</v>
       </c>
+    </row>
+    <row r="3" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="5">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>9990</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="5">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="5">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="5">
+        <v>31</v>
+      </c>
+      <c r="E8" s="3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="5">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="5">
+        <v>40</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="5">
+        <v>60</v>
+      </c>
+      <c r="E13" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="5">
+        <v>35</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="5">
+        <v>80</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3">
+        <v>12000</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="5">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="5">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="5">
+        <v>48</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="5">
+        <v>37</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="5">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="5">
+        <v>15</v>
+      </c>
+      <c r="E24" s="3">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="5">
+        <v>18</v>
+      </c>
+      <c r="E25" s="3">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="5">
+        <v>18</v>
+      </c>
+      <c r="E26" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="6">
+        <v>19</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="6">
+        <v>6</v>
+      </c>
+      <c r="E28" s="3">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="6">
+        <v>24</v>
+      </c>
+      <c r="E29" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="6">
+        <v>50</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="6">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="6">
+        <v>19</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="6">
+        <v>6</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4300</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:E33" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D549FC6F-AED8-4D85-A834-D2891A3F1910}">
+  <dimension ref="B2:G38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -620,11 +1114,11 @@
       <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="5">
         <v>5</v>
       </c>
-      <c r="E3" s="4">
-        <v>8000</v>
+      <c r="E3" s="5">
+        <v>30000</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -634,13 +1128,12 @@
       <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3">
         <v>4000</v>
       </c>
-      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
@@ -649,10 +1142,12 @@
       <c r="C5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="3">
-        <v>10</v>
-      </c>
-      <c r="E5" s="4"/>
+      <c r="D5" s="5">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3">
+        <v>12000</v>
+      </c>
     </row>
     <row r="6" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
@@ -661,10 +1156,12 @@
       <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="3">
-        <v>11</v>
-      </c>
-      <c r="E6" s="4"/>
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3000</v>
+      </c>
     </row>
     <row r="7" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
@@ -673,10 +1170,12 @@
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="5">
         <v>12</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
@@ -685,10 +1184,12 @@
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="4"/>
+      <c r="D8" s="5">
+        <v>31</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
@@ -697,22 +1198,27 @@
       <c r="C9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>3</v>
       </c>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="2:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6"/>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
@@ -721,10 +1227,12 @@
       <c r="C11" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4"/>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
@@ -733,10 +1241,12 @@
       <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4"/>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
@@ -745,10 +1255,12 @@
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4"/>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
@@ -757,10 +1269,12 @@
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4"/>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
@@ -769,10 +1283,12 @@
       <c r="C15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="3">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4"/>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
@@ -781,10 +1297,12 @@
       <c r="C16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="3">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4"/>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
@@ -793,10 +1311,12 @@
       <c r="C17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4"/>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
@@ -805,10 +1325,12 @@
       <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4"/>
+      <c r="D18" s="5">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
@@ -817,10 +1339,12 @@
       <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4"/>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
@@ -829,10 +1353,12 @@
       <c r="C20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="3">
-        <v>1</v>
-      </c>
-      <c r="E20" s="4"/>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
@@ -841,10 +1367,12 @@
       <c r="C21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="4"/>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
@@ -853,10 +1381,12 @@
       <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4"/>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
@@ -865,10 +1395,12 @@
       <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4"/>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
@@ -877,10 +1409,12 @@
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4"/>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
@@ -889,10 +1423,12 @@
       <c r="C25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D25" s="3">
-        <v>1</v>
-      </c>
-      <c r="E25" s="4"/>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
@@ -901,10 +1437,12 @@
       <c r="C26" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="3">
-        <v>1</v>
-      </c>
-      <c r="E26" s="4"/>
+      <c r="D26" s="5">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
@@ -913,10 +1451,12 @@
       <c r="C27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="3">
-        <v>1</v>
-      </c>
-      <c r="E27" s="4"/>
+      <c r="D27" s="5">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
@@ -925,10 +1465,12 @@
       <c r="C28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="4"/>
+      <c r="D28" s="5">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
@@ -937,10 +1479,12 @@
       <c r="C29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="4"/>
+      <c r="D29" s="6">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
@@ -949,10 +1493,12 @@
       <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="3">
-        <v>1</v>
-      </c>
-      <c r="E30" s="4"/>
+      <c r="D30" s="6">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
@@ -961,10 +1507,12 @@
       <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="3">
-        <v>1</v>
-      </c>
-      <c r="E31" s="4"/>
+      <c r="D31" s="6">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
@@ -973,10 +1521,12 @@
       <c r="C32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
-      <c r="E32" s="4"/>
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
@@ -985,10 +1535,12 @@
       <c r="C33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="3">
-        <v>1</v>
-      </c>
-      <c r="E33" s="4"/>
+      <c r="D33" s="6">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
@@ -997,10 +1549,12 @@
       <c r="C34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" s="4"/>
+      <c r="D34" s="6">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
@@ -1009,10 +1563,12 @@
       <c r="C35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="3">
-        <v>1</v>
-      </c>
-      <c r="E35" s="4"/>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
@@ -1021,10 +1577,12 @@
       <c r="C36" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="3">
-        <v>1</v>
-      </c>
-      <c r="E36" s="4"/>
+      <c r="D36" s="6">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
@@ -1033,10 +1591,12 @@
       <c r="C37" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="3">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4"/>
+      <c r="D37" s="6">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
@@ -1045,14 +1605,14 @@
       <c r="C38" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="4"/>
+      <c r="D38" s="6">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:E38" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>